--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -963,17 +963,17 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>3 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Parcial / PRELIM</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>✅ Listo</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Confirmar verbatim con el texto primario de la estrategia (PDF) o verificar la fuente.</t>
+          <t>Validar el puntaje propuesto por la rúbrica.</t>
         </is>
       </c>
     </row>
@@ -1287,17 +1287,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>1 (BAJA)</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Parcial / PRELIM</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>✅ Listo</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Confirmar verbatim con el texto primario de la estrategia (PDF) o verificar la fuente. · Nota: PT: solo principio en EDN, no eje en ANIA</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: validado en Valge raamat (no es eje; 'kestlik areng' = econ. de datos); PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Parcial / PRELIM</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>✅ Listo</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Confirmar verbatim con el texto primario de la estrategia (PDF) o verificar la fuente. · Nota: PT: consulta pública con resultados</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: stakeholders ('Kaasatud osapooled'), no consulta ciudadana; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>
@@ -1341,17 +1341,17 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>3 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Parcial / PRELIM</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>✅ Listo</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Confirmar verbatim con el texto primario de la estrategia (PDF) o verificar la fuente. · Nota: PT: Gob+4</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: Gob+3 (ITL/empresas + universidades + vabaühendused), p.8/12; PT: Gob+4</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>4 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Parcial / PRELIM</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>✅ Listo</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Confirmar verbatim con el texto primario de la estrategia (PDF) o verificar la fuente.</t>
+          <t>Validar el puntaje propuesto por la rúbrica.</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: validado en Valge raamat (no es eje; 'kestlik areng' = econ. de datos); PT: solo principio en EDN, no eje en ANIA</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: validado con texto primario — IA verde/ODS/herramienta de sostenibilidad/rohejalajälg; PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: stakeholders ('Kaasatud osapooled'), no consulta ciudadana; PT: consulta pública con resultados</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: 2 encuestas ómnibus (2150 residentes) + 220 entrevistas, resultados publicados; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: 2 encuestas ómnibus (2150 residentes) + 220 entrevistas, resultados publicados; PT: consulta pública con resultados</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: &gt;1 mecanismo (2 encuestas ómnibus 2150 residentes + 220 entrevistas), resultados publicados; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: Gob+3 (ITL/empresas + universidades + vabaühendused), p.8/12; PT: Gob+4</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: Gob+4 (privado + academia + ONG vabaühendused + público general/encuestas 2150), p.8/12 + PA p.6; PT: Gob+4</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: 2024, renovables total. ES/PT/DE: ERNC excl. gran hidro es menor (ver energia_*.md)</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: Energía limpia = renovables + NUCLEAR (incl. hidro). EMBER 2025, determinístico (energia_limpia_ember2025.py). Solo ES tiene nuclear (18,79%). A confirmar con CENIA</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Planilla_EE_Estonia_ILIA2026.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica.</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: SG: validado (NAIS se revisa 1.0→2.0→Update 2026; métricas de proyecto)</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: validado con texto primario — IA verde/ODS/herramienta de sostenibilidad/rohejalajälg; PT: solo principio en EDN, no eje en ANIA</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: validado (IA verde/ODS); SG: validado (resource-efficient/'green' AI, Green Data Centre Roadmap); PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: &gt;1 mecanismo (2 encuestas ómnibus 2150 residentes + 220 entrevistas), resultados publicados; PT: consulta pública con resultados</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: &gt;1 mecanismo (encuestas 2150 + 220 entrevistas); SG: sin mecanismo ciudadano (consulta solo a representantes del ecosistema → cuenta en 121); PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: Gob+4 (privado + academia + ONG vabaühendused + público general/encuestas 2150), p.8/12 + PA p.6; PT: Gob+4</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: EE: Gob+4 (privado+academia+ONG+público); SG: Gob+3 (industria+academia+non-profit; SCAI/RAISE.SG); PT: Gob+4</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica.</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: SG: validado — Whole-of-Nation + Tripartite (Gob/NTUC/empleadores) + AI Verify Foundation (non-profit)</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Validar el puntaje propuesto por la rúbrica.</t>
+          <t>Validar el puntaje propuesto por la rúbrica. · Nota: SG: validado — enfoque 'risk-based, tiered' (NAIS 2.0 p.59; Update p.17)</t>
         </is>
       </c>
     </row>
